--- a/artfynd/A 49552-2022 artfynd.xlsx
+++ b/artfynd/A 49552-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119802037</v>
+        <v>119802041</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -773,21 +773,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -804,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119802041</v>
+        <v>119802037</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -902,6 +887,21 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 49552-2022 artfynd.xlsx
+++ b/artfynd/A 49552-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119802041</v>
       </c>
       <c r="B2" t="n">
-        <v>90905</v>
+        <v>90923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>119802037</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49552-2022 artfynd.xlsx
+++ b/artfynd/A 49552-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119802041</v>
+        <v>119802037</v>
       </c>
       <c r="B2" t="n">
-        <v>90923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -773,6 +768,21 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -789,37 +799,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119802037</v>
+        <v>119802041</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -887,21 +892,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 49552-2022 artfynd.xlsx
+++ b/artfynd/A 49552-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119802037</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,8 +915,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119802041</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>